--- a/sampleprojects/CHIP/excel/CHIP_map.xlsx
+++ b/sampleprojects/CHIP/excel/CHIP_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>MAP: CHIP</t>
   </si>
@@ -125,6 +125,33 @@
   </si>
   <si>
     <t>earned</t>
+  </si>
+  <si>
+    <t>## CREATE ENTITIES (entity | tag | id | list)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>constants</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>## ENTITIES (name | number: 1 or *)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>## INITIALIZATION (entity | push)</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -909,6 +936,256 @@
         <v>19</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
